--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,19 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571A2DAC-B1F9-43A8-916A-31D205D69A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACEF23C-7DC0-4E7D-9B40-97B4ED82FB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="0" windowWidth="20370" windowHeight="10770" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano individualus IP" sheetId="1" r:id="rId1"/>
     <sheet name="Potinkliai" sheetId="2" r:id="rId2"/>
     <sheet name="IP adresai" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -30,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="122">
   <si>
     <t>Individualus ipv4:</t>
   </si>
@@ -47,12 +56,6 @@
     <t>Vieta</t>
   </si>
   <si>
-    <t>24.40.7.1</t>
-  </si>
-  <si>
-    <t>24.40.7.64</t>
-  </si>
-  <si>
     <t>Administracija</t>
   </si>
   <si>
@@ -65,9 +68,6 @@
     <t>Potinklis</t>
   </si>
   <si>
-    <t>Paskirtis (Kur priklauso konferencijų salė)</t>
-  </si>
-  <si>
     <t>Reikalinga IP</t>
   </si>
   <si>
@@ -83,97 +83,18 @@
     <t>Subnet 1</t>
   </si>
   <si>
-    <t>IT Centras + Konferencijų salė</t>
-  </si>
-  <si>
-    <t>~60</t>
-  </si>
-  <si>
-    <t>24.40.7.0</t>
-  </si>
-  <si>
-    <t>255.255.255.192</t>
-  </si>
-  <si>
     <t>Subnet 2</t>
   </si>
   <si>
-    <r>
-      <t>2 a. Centrai</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Dizainas/Mult.)</t>
-    </r>
-  </si>
-  <si>
-    <t>~42</t>
-  </si>
-  <si>
-    <t>24.40.7.65</t>
-  </si>
-  <si>
     <t>Subnet 3</t>
   </si>
   <si>
-    <r>
-      <t>1 a. Auditorijos</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (12+14)</t>
-    </r>
-  </si>
-  <si>
-    <t>~30</t>
-  </si>
-  <si>
-    <t>24.40.7.128</t>
-  </si>
-  <si>
-    <t>255.255.255.224</t>
-  </si>
-  <si>
-    <t>24.40.7.129</t>
-  </si>
-  <si>
     <t>Subnet 4</t>
   </si>
   <si>
-    <t>~20</t>
-  </si>
-  <si>
-    <t>24.40.7.160</t>
-  </si>
-  <si>
-    <t>24.40.7.161</t>
-  </si>
-  <si>
     <t>Subnet 5</t>
   </si>
   <si>
-    <t>~12</t>
-  </si>
-  <si>
-    <t>24.40.7.192</t>
-  </si>
-  <si>
-    <t>255.255.255.240</t>
-  </si>
-  <si>
-    <t>24.40.7.193</t>
-  </si>
-  <si>
     <t>Subnet 6</t>
   </si>
   <si>
@@ -183,12 +104,6 @@
     <t>~10</t>
   </si>
   <si>
-    <t>24.40.7.208</t>
-  </si>
-  <si>
-    <t>24.40.7.209</t>
-  </si>
-  <si>
     <t>IPv4</t>
   </si>
   <si>
@@ -282,9 +197,6 @@
     <t>fa0</t>
   </si>
   <si>
-    <t>Switch 2960-24TT ( fa 0/1 sujungta su core switch G 1/0/5)</t>
-  </si>
-  <si>
     <t>Access Point (sujungta su switch 2960 fa 0/2)</t>
   </si>
   <si>
@@ -312,15 +224,9 @@
     <t>Switch 2960-24TT antras (fa 0/1 sujungta su Switch 2960-24TT pirmas fa 0/2)</t>
   </si>
   <si>
-    <t>Access Point (sujungta su Switch 2960-24TT pirmas fa 0/2)</t>
-  </si>
-  <si>
     <t>Access Point (sujungta su Switch 2960-24TT pirmas fa 0/3)</t>
   </si>
   <si>
-    <t>Camera (sujungta su Switch 2960-24TT pirmas fa 0/3)</t>
-  </si>
-  <si>
     <t>Camera (sujungta su Switch 2960-24TT pirmas fa 0/4)</t>
   </si>
   <si>
@@ -342,10 +248,163 @@
     <t>Switch 2960-24TT (fa 0/1 sujungta su core switch G 1/0/9)</t>
   </si>
   <si>
-    <t>PC0 pirmas (sujungta su Switch 2960-24TT pirmas fa 0/4)</t>
-  </si>
-  <si>
-    <t>PC1 paskutinis (sujungta su Switch 2960-24TT pirmas fa 0/5)</t>
+    <t>Switch 2960-24TT (fa 0/1 sujungta su core switch G 1/0/5)</t>
+  </si>
+  <si>
+    <t>Testavimo centras</t>
+  </si>
+  <si>
+    <t>Switch Empty su G 0/1 ir G 1/1(G 0/1 sujungta su core switch G 1/1/1 per optinį laidą)</t>
+  </si>
+  <si>
+    <t>Switch 2960-24TT (fa 0/1 sujungta su Switch Empty su G 1/1)</t>
+  </si>
+  <si>
+    <t>Access Point (sujungta su Switch 2960-24TT fa 0/2)</t>
+  </si>
+  <si>
+    <t>Camera (sujungta su Switch 2960-24TT fa 0/3)</t>
+  </si>
+  <si>
+    <t>PC0 pirmas (sujungta su Switch 2960-24TT fa 0/4)</t>
+  </si>
+  <si>
+    <t>PC1 paskutinis (sujungta su Switch 2960-24TT fa 0/5)</t>
+  </si>
+  <si>
+    <t>Išmaniųjų technologijų mokymo centras</t>
+  </si>
+  <si>
+    <t>Serverinė</t>
+  </si>
+  <si>
+    <t>Switch Empty su G 0/1 ir G 1/1(G 0/1 sujungta su core switch G 1/1/2 per optinį laidą)</t>
+  </si>
+  <si>
+    <t>Camera (sujungta su Switch 2960-24TT fa 0/13)</t>
+  </si>
+  <si>
+    <t>Carbon monoxide detector</t>
+  </si>
+  <si>
+    <t>DNS</t>
+  </si>
+  <si>
+    <t>Wireless0</t>
+  </si>
+  <si>
+    <t>Carbon dioxide detector</t>
+  </si>
+  <si>
+    <t>Smoke detector</t>
+  </si>
+  <si>
+    <t>Motion detector</t>
+  </si>
+  <si>
+    <t>Dėstytojų kambarys</t>
+  </si>
+  <si>
+    <t>Switch 2960-24TT (fa 0/1 sujungta su Switch iš serverinės su fa 0/2)</t>
+  </si>
+  <si>
+    <t>Budėtojų apsaugos kambarys</t>
+  </si>
+  <si>
+    <t>Switch 2960-24TT (fa 0/1 sujungta su Switch iš serverinės su fa 0/4)</t>
+  </si>
+  <si>
+    <t>IoT registracijos serveris (fa0 sujungta su Switch 2960-24TT fa 0/2)</t>
+  </si>
+  <si>
+    <t>Access Point (sujungta su Switch 2960-24TT fa 0/3)</t>
+  </si>
+  <si>
+    <t>Camera (sujungta su Switch 2960-24TT fa 0/4)</t>
+  </si>
+  <si>
+    <t>PC0 pirmas (sujungta su Switch 2960-24TT fa 0/5)</t>
+  </si>
+  <si>
+    <t>PC1 paskutinis (sujungta su Switch 2960-24TT fa 0/6)</t>
+  </si>
+  <si>
+    <t>Elektronikos dirbtuvės</t>
+  </si>
+  <si>
+    <t>Switch 2960-24TT pirmas (fa 0/1 sujungta su Switch iš serverinės su fa 0/3)</t>
+  </si>
+  <si>
+    <t>Switch 2960-24TT antras (fa 0/1 sujungta su Switch 2960-24TT pirmas su fa 0/2)</t>
+  </si>
+  <si>
+    <t>Thermostat</t>
+  </si>
+  <si>
+    <t>Temperature monitor</t>
+  </si>
+  <si>
+    <t>Konferencijų salė</t>
+  </si>
+  <si>
+    <t>Salė</t>
+  </si>
+  <si>
+    <t>Camera (fa0 sujungta su Switch iš išmaniųjų technologijų serverinės su fa 0/14)</t>
+  </si>
+  <si>
+    <t>Access Point 1 (sujungta su Switch iš išmaniųjų technologijų serverinės su fa 0/5)</t>
+  </si>
+  <si>
+    <t>Access Point 2 (sujungta su Switch iš išmaniųjų technologijų serverinės su fa 0/6)</t>
+  </si>
+  <si>
+    <t>Access Point 3 (sujungta su Switch iš išmaniųjų technologijų serverinės su fa 0/7)</t>
+  </si>
+  <si>
+    <t>Access Point 4 (sujungta su Switch iš išmaniųjų technologijų serverinės su fa 0/8)</t>
+  </si>
+  <si>
+    <t>Access Point 5 (sujungta su Switch iš išmaniųjų technologijų serverinės su fa 0/9)</t>
+  </si>
+  <si>
+    <t>Access Point 6 (sujungta su Switch iš išmaniųjų technologijų serverinės su fa 0/10)</t>
+  </si>
+  <si>
+    <t>Access Point 7 (sujungta su Switch iš išmaniųjų technologijų serverinės su fa 0/11)</t>
+  </si>
+  <si>
+    <t>Access Point 8 (sujungta su Switch iš išmaniųjų technologijų serverinės su fa 0/12)</t>
+  </si>
+  <si>
+    <t>Smartphone0 (sujungta su vienu iš Access Point)</t>
+  </si>
+  <si>
+    <t>Smartphone1 (sujungta su vienu iš Access Point)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTK antras aukštas </t>
+  </si>
+  <si>
+    <t>MTK pirmas aukštas. administracija, auditorija 1, auditorija 2</t>
+  </si>
+  <si>
+    <t>MTK pirmas aukštas. Serverinė</t>
+  </si>
+  <si>
+    <t>Paskirtis</t>
+  </si>
+  <si>
+    <t>~50</t>
+  </si>
+  <si>
+    <t>~25</t>
+  </si>
+  <si>
+    <t>~40</t>
+  </si>
+  <si>
+    <t>Išmaniųjų technologijų centras. Budėtojų apsaugos kambarys.</t>
   </si>
 </sst>
 </file>
@@ -444,6 +503,24 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5ADA9601-1BF5-4D34-9F9C-76694FF6FDD6}" name="Table2" displayName="Table2" ref="A1:I95" totalsRowShown="0">
+  <autoFilter ref="A1:I95" xr:uid="{5ADA9601-1BF5-4D34-9F9C-76694FF6FDD6}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{36743873-96E0-4265-9AA8-5004B79F0BD5}" name="Vieta"/>
+    <tableColumn id="2" xr3:uid="{A21D75B4-A791-41B9-8A61-2BF2AAC91809}" name="Patalpa"/>
+    <tableColumn id="3" xr3:uid="{49552E90-F042-4AB0-83C3-5A6D6EFDCDE3}" name="Prietaisas"/>
+    <tableColumn id="4" xr3:uid="{F539A714-0A13-45EF-A36D-385D49AE5184}" name="Interfeisas"/>
+    <tableColumn id="5" xr3:uid="{7C8FE78E-2FE6-49DB-B37F-085628FFA88D}" name="IPv4"/>
+    <tableColumn id="6" xr3:uid="{E8A8768B-0CB0-4109-81EC-2C1B304E62A8}" name="Subnet Mask"/>
+    <tableColumn id="7" xr3:uid="{41793646-7A1D-43B1-B189-F1FF5F63166F}" name="Default Gateway"/>
+    <tableColumn id="8" xr3:uid="{86C36F71-B853-401A-8FF9-6692CF5F35DC}" name="IPv6"/>
+    <tableColumn id="9" xr3:uid="{9B9DC71C-D985-44C9-A7E3-F93F98A8E212}" name="DNS"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -744,7 +821,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" customWidth="1"/>
     <col min="3" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="18.140625" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
@@ -755,145 +832,109 @@
     <col min="14" max="14" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="45" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>30</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -902,593 +943,1369 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DED76EF4-F36D-4798-A3D9-ABBA77471550}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="71.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.42578125" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
     <col min="8" max="8" width="46.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="F1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="D13" t="s">
         <v>48</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
         <v>54</v>
       </c>
-      <c r="C18" t="s">
-        <v>79</v>
-      </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" t="s">
         <v>49</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
         <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="D35" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B51" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>77</v>
+      </c>
+      <c r="B55" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B58" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" t="s">
+        <v>87</v>
+      </c>
+      <c r="C60" t="s">
+        <v>84</v>
+      </c>
+      <c r="D60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>77</v>
+      </c>
+      <c r="B61" t="s">
+        <v>87</v>
+      </c>
+      <c r="C61" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62" t="s">
+        <v>86</v>
+      </c>
+      <c r="D62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" t="s">
+        <v>90</v>
+      </c>
+      <c r="D63" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" t="s">
+        <v>89</v>
+      </c>
+      <c r="C64" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>77</v>
+      </c>
+      <c r="B65" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" t="s">
+        <v>92</v>
+      </c>
+      <c r="D65" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+      <c r="B66" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" t="s">
         <v>93</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D66" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" t="s">
+        <v>84</v>
+      </c>
+      <c r="D70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" t="s">
+        <v>85</v>
+      </c>
+      <c r="D71" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" t="s">
+        <v>86</v>
+      </c>
+      <c r="D72" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" t="s">
         <v>97</v>
       </c>
-      <c r="D40" t="s">
-        <v>75</v>
+      <c r="D73" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74" t="s">
+        <v>98</v>
+      </c>
+      <c r="D74" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75" t="s">
+        <v>61</v>
+      </c>
+      <c r="D75" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" t="s">
+        <v>62</v>
+      </c>
+      <c r="D76" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" t="s">
+        <v>63</v>
+      </c>
+      <c r="D77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" t="s">
+        <v>64</v>
+      </c>
+      <c r="D78" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>96</v>
+      </c>
+      <c r="C79" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" t="s">
+        <v>84</v>
+      </c>
+      <c r="D80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>77</v>
+      </c>
+      <c r="B81" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81" t="s">
+        <v>85</v>
+      </c>
+      <c r="D81" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>77</v>
+      </c>
+      <c r="B82" t="s">
+        <v>96</v>
+      </c>
+      <c r="C82" t="s">
+        <v>86</v>
+      </c>
+      <c r="D82" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>77</v>
+      </c>
+      <c r="B83" t="s">
+        <v>96</v>
+      </c>
+      <c r="C83" t="s">
+        <v>99</v>
+      </c>
+      <c r="D83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>77</v>
+      </c>
+      <c r="B84" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>101</v>
+      </c>
+      <c r="B85" t="s">
+        <v>102</v>
+      </c>
+      <c r="C85" t="s">
+        <v>103</v>
+      </c>
+      <c r="D85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>101</v>
+      </c>
+      <c r="B86" t="s">
+        <v>102</v>
+      </c>
+      <c r="C86" t="s">
+        <v>104</v>
+      </c>
+      <c r="D86" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>101</v>
+      </c>
+      <c r="B87" t="s">
+        <v>102</v>
+      </c>
+      <c r="C87" t="s">
+        <v>105</v>
+      </c>
+      <c r="D87" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>101</v>
+      </c>
+      <c r="B88" t="s">
+        <v>102</v>
+      </c>
+      <c r="C88" t="s">
+        <v>106</v>
+      </c>
+      <c r="D88" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>101</v>
+      </c>
+      <c r="B89" t="s">
+        <v>102</v>
+      </c>
+      <c r="C89" t="s">
+        <v>107</v>
+      </c>
+      <c r="D89" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" t="s">
+        <v>102</v>
+      </c>
+      <c r="C90" t="s">
+        <v>108</v>
+      </c>
+      <c r="D90" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" t="s">
+        <v>102</v>
+      </c>
+      <c r="C91" t="s">
+        <v>109</v>
+      </c>
+      <c r="D91" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>101</v>
+      </c>
+      <c r="B92" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D92" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" t="s">
+        <v>111</v>
+      </c>
+      <c r="D93" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" t="s">
+        <v>102</v>
+      </c>
+      <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" t="s">
+        <v>102</v>
+      </c>
+      <c r="C95" t="s">
+        <v>113</v>
+      </c>
+      <c r="D95" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACEF23C-7DC0-4E7D-9B40-97B4ED82FB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FAFB58-8DE2-43D0-B981-6A27DE0DCEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="0" windowWidth="20370" windowHeight="10770" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano individualus IP" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="142">
   <si>
     <t>Individualus ipv4:</t>
   </si>
@@ -77,33 +77,6 @@
     <t>Kaukė (Subnet Mask)</t>
   </si>
   <si>
-    <t>Gateway</t>
-  </si>
-  <si>
-    <t>Subnet 1</t>
-  </si>
-  <si>
-    <t>Subnet 2</t>
-  </si>
-  <si>
-    <t>Subnet 3</t>
-  </si>
-  <si>
-    <t>Subnet 4</t>
-  </si>
-  <si>
-    <t>Subnet 5</t>
-  </si>
-  <si>
-    <t>Subnet 6</t>
-  </si>
-  <si>
-    <t>Serveriai ir IoT</t>
-  </si>
-  <si>
-    <t>~10</t>
-  </si>
-  <si>
     <t>IPv4</t>
   </si>
   <si>
@@ -386,25 +359,112 @@
     <t xml:space="preserve">MTK antras aukštas </t>
   </si>
   <si>
-    <t>MTK pirmas aukštas. administracija, auditorija 1, auditorija 2</t>
-  </si>
-  <si>
-    <t>MTK pirmas aukštas. Serverinė</t>
-  </si>
-  <si>
     <t>Paskirtis</t>
   </si>
   <si>
     <t>~50</t>
   </si>
   <si>
-    <t>~25</t>
-  </si>
-  <si>
-    <t>~40</t>
-  </si>
-  <si>
-    <t>Išmaniųjų technologijų centras. Budėtojų apsaugos kambarys.</t>
+    <t>Konferenciju sale</t>
+  </si>
+  <si>
+    <t>~400</t>
+  </si>
+  <si>
+    <t>VLAN 1</t>
+  </si>
+  <si>
+    <t>VLAN 2</t>
+  </si>
+  <si>
+    <t>VLAN 3</t>
+  </si>
+  <si>
+    <t>VLAN 4</t>
+  </si>
+  <si>
+    <t>VLAN 5</t>
+  </si>
+  <si>
+    <t>VLAN 6</t>
+  </si>
+  <si>
+    <t>VLAN 7</t>
+  </si>
+  <si>
+    <t>172.16.0.0</t>
+  </si>
+  <si>
+    <t>/23</t>
+  </si>
+  <si>
+    <t>~20</t>
+  </si>
+  <si>
+    <t>Išmaniųjų t. serverine, budetoju ir destytoju kambariai</t>
+  </si>
+  <si>
+    <t>a1, a2, m, d, ed</t>
+  </si>
+  <si>
+    <t>tc</t>
+  </si>
+  <si>
+    <t>dst, bd</t>
+  </si>
+  <si>
+    <t>pop mdf serv</t>
+  </si>
+  <si>
+    <t>ism serv</t>
+  </si>
+  <si>
+    <t>Elektronikos dirbtuves ir egzaminavimo centras</t>
+  </si>
+  <si>
+    <t>centrai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTK autidorija1, auditorija2 </t>
+  </si>
+  <si>
+    <t>/27</t>
+  </si>
+  <si>
+    <t>MTK serverine</t>
+  </si>
+  <si>
+    <t>/28</t>
+  </si>
+  <si>
+    <t>MTK antras auktas</t>
+  </si>
+  <si>
+    <t>MTK administracija</t>
+  </si>
+  <si>
+    <t>/26</t>
+  </si>
+  <si>
+    <t>sunaudota ip</t>
+  </si>
+  <si>
+    <t>24.40.7.0</t>
+  </si>
+  <si>
+    <t>24.40.7.64</t>
+  </si>
+  <si>
+    <t>24.40.7.128</t>
+  </si>
+  <si>
+    <t>24.40.7.160</t>
+  </si>
+  <si>
+    <t>24.40.7.192</t>
+  </si>
+  <si>
+    <t>24.40.7.208</t>
   </si>
 </sst>
 </file>
@@ -474,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -486,6 +546,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -817,7 +886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1A8AE0-266F-4AC2-9C4A-1378C1EDC2C1}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -825,6 +894,7 @@
     <col min="3" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="18.140625" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" customWidth="1"/>
     <col min="10" max="10" width="22.85546875" customWidth="1"/>
     <col min="11" max="11" width="40.7109375" customWidth="1"/>
     <col min="12" max="12" width="20.28515625" customWidth="1"/>
@@ -837,7 +907,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>9</v>
@@ -849,95 +919,364 @@
         <v>11</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="4"/>
+        <v>126</v>
+      </c>
+      <c r="C3" s="3">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="4">
+        <v>64</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="4"/>
+        <v>132</v>
+      </c>
+      <c r="C4" s="3">
+        <v>45</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="4">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="3">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5" s="4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="4"/>
+      <c r="D6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="4">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="3">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="4">
+        <f>SUM(F3:F8)</f>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
+        <v>121</v>
+      </c>
+      <c r="K17">
+        <f>30 + 25 + 20 + 17</f>
+        <v>92</v>
+      </c>
+      <c r="L17">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K18">
+        <v>25</v>
+      </c>
+      <c r="L18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
+        <v>123</v>
+      </c>
+      <c r="K19">
+        <v>25</v>
+      </c>
+      <c r="L19">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>124</v>
+      </c>
+      <c r="K20">
+        <v>10</v>
+      </c>
+      <c r="L20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="4"/>
+      <c r="J21" t="s">
+        <v>125</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>14</v>
+      </c>
+      <c r="E23">
+        <v>40</v>
+      </c>
+      <c r="F23">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="4"/>
+      <c r="H23">
+        <v>16</v>
+      </c>
+      <c r="I23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <v>16</v>
+      </c>
+      <c r="F24">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C31">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <f>SUM(D23:D28)</f>
+        <v>30</v>
+      </c>
+      <c r="E31">
+        <v>40</v>
+      </c>
+      <c r="F31">
+        <f>SUM(F23:F27)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C33">
+        <v>16</v>
+      </c>
+      <c r="D33">
+        <v>32</v>
+      </c>
+      <c r="E33">
+        <v>64</v>
+      </c>
+      <c r="F33">
+        <v>64</v>
+      </c>
+      <c r="G33">
+        <v>32</v>
+      </c>
+      <c r="H33">
+        <v>16</v>
+      </c>
+      <c r="I33">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F12">
+    <sortCondition ref="A1:A12"/>
+  </sortState>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -964,571 +1303,571 @@
         <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
         <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D36" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D38" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" t="s">
         <v>66</v>
       </c>
-      <c r="C39" t="s">
-        <v>75</v>
-      </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,13 +1875,13 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1550,13 +1889,13 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1564,13 +1903,13 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1578,13 +1917,13 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1592,13 +1931,13 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1606,699 +1945,699 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D48" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D49" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D51" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C52" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D52" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" t="s">
         <v>77</v>
       </c>
-      <c r="B53" t="s">
-        <v>78</v>
-      </c>
-      <c r="C53" t="s">
-        <v>86</v>
-      </c>
       <c r="D53" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D54" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D55" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D58" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D59" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D60" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D61" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" t="s">
         <v>77</v>
       </c>
-      <c r="B62" t="s">
-        <v>87</v>
-      </c>
-      <c r="C62" t="s">
-        <v>86</v>
-      </c>
       <c r="D62" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D63" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C65" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D65" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D66" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D68" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D69" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D70" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D71" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>68</v>
+      </c>
+      <c r="B72" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" t="s">
         <v>77</v>
       </c>
-      <c r="B72" t="s">
-        <v>89</v>
-      </c>
-      <c r="C72" t="s">
-        <v>86</v>
-      </c>
       <c r="D72" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C73" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D73" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C74" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D74" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D75" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C76" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D76" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D77" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C78" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D78" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D80" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C81" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>68</v>
+      </c>
+      <c r="B82" t="s">
+        <v>87</v>
+      </c>
+      <c r="C82" t="s">
         <v>77</v>
       </c>
-      <c r="B82" t="s">
-        <v>96</v>
-      </c>
-      <c r="C82" t="s">
-        <v>86</v>
-      </c>
       <c r="D82" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D83" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D84" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C85" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D85" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C86" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D86" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C87" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D87" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C88" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D88" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D89" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C90" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D90" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C91" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D91" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" t="s">
+        <v>93</v>
+      </c>
+      <c r="C92" t="s">
         <v>101</v>
       </c>
-      <c r="B92" t="s">
-        <v>102</v>
-      </c>
-      <c r="C92" t="s">
-        <v>110</v>
-      </c>
       <c r="D92" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>93</v>
+      </c>
+      <c r="C93" t="s">
         <v>102</v>
       </c>
-      <c r="C93" t="s">
-        <v>111</v>
-      </c>
       <c r="D93" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D94" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B95" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D95" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FAFB58-8DE2-43D0-B981-6A27DE0DCEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30239802-7DCE-4195-8D0D-021EAF7F1D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20520" yWindow="6585" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano individualus IP" sheetId="1" r:id="rId1"/>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30239802-7DCE-4195-8D0D-021EAF7F1D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6CEBDA-01AC-4A3E-A118-665BDD4F0FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="6585" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20265" yWindow="6735" windowWidth="20370" windowHeight="10770" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano individualus IP" sheetId="1" r:id="rId1"/>
@@ -371,9 +371,6 @@
     <t>~400</t>
   </si>
   <si>
-    <t>VLAN 1</t>
-  </si>
-  <si>
     <t>VLAN 2</t>
   </si>
   <si>
@@ -465,6 +462,9 @@
   </si>
   <si>
     <t>24.40.7.208</t>
+  </si>
+  <si>
+    <t>VLAN 8</t>
   </si>
 </sst>
 </file>
@@ -919,12 +919,12 @@
         <v>11</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>108</v>
@@ -933,10 +933,10 @@
         <v>109</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -944,19 +944,19 @@
     </row>
     <row r="3" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3">
         <v>60</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F3" s="4">
         <v>64</v>
@@ -964,19 +964,19 @@
     </row>
     <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3">
         <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="4">
         <v>64</v>
@@ -984,19 +984,19 @@
     </row>
     <row r="5" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" s="3">
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F5" s="4">
         <v>32</v>
@@ -1004,19 +1004,19 @@
     </row>
     <row r="6" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F6" s="4">
         <v>32</v>
@@ -1024,19 +1024,19 @@
     </row>
     <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="3">
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F7" s="4">
         <v>16</v>
@@ -1044,19 +1044,19 @@
     </row>
     <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="3">
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F8" s="4">
         <v>16</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="J17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K17">
         <f>30 + 25 + 20 + 17</f>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="J18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K18">
         <v>25</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="J19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K19">
         <v>25</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K20">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="4"/>
       <c r="J21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K21">
         <v>10</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C23">
         <v>10</v>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6CEBDA-01AC-4A3E-A118-665BDD4F0FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9C2F8F-AA58-4C66-BA21-3259269FEB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20265" yWindow="6735" windowWidth="20370" windowHeight="10770" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20520" yWindow="6585" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano individualus IP" sheetId="1" r:id="rId1"/>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9C2F8F-AA58-4C66-BA21-3259269FEB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999817C2-2FBA-421D-9691-881B98F62852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="6585" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20520" yWindow="6585" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano individualus IP" sheetId="1" r:id="rId1"/>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999817C2-2FBA-421D-9691-881B98F62852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4863725F-7BDB-4A67-B5A9-81F9BBD13972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="6585" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano individualus IP" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="157">
   <si>
     <t>Individualus ipv4:</t>
   </si>
@@ -465,6 +465,51 @@
   </si>
   <si>
     <t>VLAN 8</t>
+  </si>
+  <si>
+    <t>Router(config-ext-nacl)# deny ip any 24.40.7.192 0.0.0.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Draudžiama patekti į Budėtojus/IoT (24.40.7.160/27) </t>
+  </si>
+  <si>
+    <t>Router(config-ext-nacl)# deny ip any 24.40.7.160 0.0.0.31</t>
+  </si>
+  <si>
+    <t># 3. Leidžiama visą kitą srautą (Internetą, WEB serverį, DHCP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Router(config-ext-nacl)# permit ip any any </t>
+  </si>
+  <si>
+    <t># 1. Draudžiama patekti į Administraciją (24.40.7.192/28)</t>
+  </si>
+  <si>
+    <t>Router(config)# ip access-list extended BLOKAVIMAS_AUDITORIJOMS</t>
+  </si>
+  <si>
+    <t>acl ipv4</t>
+  </si>
+  <si>
+    <t>acl ipv6</t>
+  </si>
+  <si>
+    <t>Router(config)# ipv6 access-list BLOKAVIMAS_V6</t>
+  </si>
+  <si>
+    <t># Draudžiam į Administracijos (VLAN 6) ir IoT (VLAN 5) IPv6 tinklus</t>
+  </si>
+  <si>
+    <t>Router(config-ipv6-acl)# deny ipv6 any 2001:DB8:ACAD:6::/64</t>
+  </si>
+  <si>
+    <t>Router(config-ipv6-acl)# deny ipv6 any 2001:DB8:ACAD:5::/64</t>
+  </si>
+  <si>
+    <t># Leidžiam visa kita</t>
+  </si>
+  <si>
+    <t>Router(config-ipv6-acl)# permit ipv6 any any</t>
   </si>
 </sst>
 </file>
@@ -534,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -556,6 +601,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -855,11 +903,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="11.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="66.42578125" customWidth="1"/>
+    <col min="2" max="2" width="59.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -876,6 +924,67 @@
       </c>
       <c r="B2" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4863725F-7BDB-4A67-B5A9-81F9BBD13972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674B82B8-E473-44F0-8E4D-2B1EECF8CBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20520" yWindow="6585" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano individualus IP" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="161">
   <si>
     <t>Individualus ipv4:</t>
   </si>
@@ -510,6 +510,18 @@
   </si>
   <si>
     <t>Router(config-ipv6-acl)# permit ipv6 any any</t>
+  </si>
+  <si>
+    <t>Router(config)# interface g0/0.2</t>
+  </si>
+  <si>
+    <t>Router(config-subif)# ip access-group BLOKAVIMAS_AUDITORIJOMS in</t>
+  </si>
+  <si>
+    <t>Router(config-subif)# ipv6 traffic-filter BLOKAVIMAS_V6 in</t>
+  </si>
+  <si>
+    <t>pritaikau tai vlan 2, 3, 4 ir 8</t>
   </si>
 </sst>
 </file>
@@ -903,14 +915,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="11.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.42578125" customWidth="1"/>
     <col min="2" max="2" width="59.140625" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -918,7 +931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -926,44 +939,56 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>148</v>
       </c>
       <c r="B6" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>147</v>
       </c>
       <c r="B7" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>142</v>
       </c>
       <c r="B8" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>143</v>
       </c>
       <c r="B9" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>144</v>
       </c>
@@ -971,7 +996,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>145</v>
       </c>
@@ -979,7 +1004,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>146</v>
       </c>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A20D074-4D94-4285-95CD-420989C6C2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3552C8-9DB1-43B1-A34B-B769FAF37685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Desktop\mokslai\semestras 4\komp-tinklai\L2B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Desktop\Mokslai\komp tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3552C8-9DB1-43B1-A34B-B769FAF37685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AD9063-CB2A-4EBB-94C0-DC1CC18B6F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mano individualus IP" sheetId="1" r:id="rId1"/>
+    <sheet name="ACL tasyklės" sheetId="1" r:id="rId1"/>
     <sheet name="Potinkliai" sheetId="2" r:id="rId2"/>
     <sheet name="Statiniai IP adresai" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -803,14 +803,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="11.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="66.42578125" customWidth="1"/>
-    <col min="2" max="2" width="59.140625" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" customWidth="1"/>
+    <col min="1" max="1" width="66.44140625" customWidth="1"/>
+    <col min="2" max="2" width="59.109375" customWidth="1"/>
+    <col min="3" max="3" width="35.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -826,12 +826,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -842,7 +842,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>44</v>
       </c>
@@ -853,7 +853,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -864,7 +864,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -875,7 +875,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -883,7 +883,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -891,7 +891,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -908,22 +908,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1A8AE0-266F-4AC2-9C4A-1378C1EDC2C1}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" customWidth="1"/>
     <col min="3" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="22.85546875" customWidth="1"/>
-    <col min="11" max="11" width="40.7109375" customWidth="1"/>
-    <col min="12" max="12" width="20.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
-    <col min="14" max="14" width="28.85546875" customWidth="1"/>
+    <col min="7" max="8" width="9.109375" customWidth="1"/>
+    <col min="10" max="10" width="22.88671875" customWidth="1"/>
+    <col min="11" max="11" width="40.6640625" customWidth="1"/>
+    <col min="12" max="12" width="20.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="28.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -943,7 +943,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -983,7 +983,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>18</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="14"/>
@@ -1092,7 +1092,7 @@
       <c r="F9" s="15"/>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -1101,7 +1101,7 @@
       <c r="F10" s="7"/>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -1110,7 +1110,7 @@
       <c r="F11" s="7"/>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -1119,7 +1119,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -1128,7 +1128,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -1136,7 +1136,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
@@ -1144,7 +1144,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="6"/>
@@ -1165,19 +1165,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DED76EF4-F36D-4798-A3D9-ABBA77471550}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.5703125" customWidth="1"/>
-    <col min="5" max="5" width="39.85546875" customWidth="1"/>
-    <col min="6" max="6" width="40.42578125" customWidth="1"/>
+    <col min="1" max="1" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.5546875" customWidth="1"/>
+    <col min="5" max="5" width="39.88671875" customWidth="1"/>
+    <col min="6" max="6" width="40.44140625" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="46.28515625" customWidth="1"/>
+    <col min="8" max="8" width="46.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>74</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>76</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>83</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>90</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>95</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>96</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>98</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>101</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>102</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>104</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>106</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>109</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>111</v>
       </c>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Desktop\Mokslai\komp tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AD9063-CB2A-4EBB-94C0-DC1CC18B6F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E83FCA-AF92-40BB-95BC-BB28FC883452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ACL tasyklės" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
   <si>
     <t>Individualus ipv4:</t>
   </si>
@@ -375,6 +375,15 @@
   </si>
   <si>
     <t>Konferencijų salė Switch</t>
+  </si>
+  <si>
+    <t>sutvarkyti detektorius</t>
+  </si>
+  <si>
+    <t>jei suveikia detektoriai tai turi isijungti sirena</t>
+  </si>
+  <si>
+    <t>judesio daviklis rcu controller prijungti mtk pastate</t>
   </si>
 </sst>
 </file>
@@ -907,7 +916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1A8AE0-266F-4AC2-9C4A-1378C1EDC2C1}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
@@ -923,7 +932,7 @@
     <col min="14" max="14" width="28.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -943,7 +952,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -963,7 +972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -983,7 +992,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1003,7 +1012,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1023,7 +1032,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1043,7 +1052,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1063,7 +1072,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>18</v>
       </c>
@@ -1083,7 +1092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="14"/>
@@ -1092,7 +1101,7 @@
       <c r="F9" s="15"/>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -1101,7 +1110,7 @@
       <c r="F10" s="7"/>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -1110,7 +1119,7 @@
       <c r="F11" s="7"/>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -1119,7 +1128,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -1128,7 +1137,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -1136,13 +1145,26 @@
       <c r="E14" s="5"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="7"/>
+      <c r="H15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>

--- a/L2B/Adresai.xlsx
+++ b/L2B/Adresai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Desktop\Mokslai\komp tinklai\L2B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E83FCA-AF92-40BB-95BC-BB28FC883452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245EDC0F-7674-4828-8661-8640150BF3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
